--- a/experiments/prompt-tuning/hc+ft/Results/FLICKR_QWEN/Flickr_prompt01.xlsx
+++ b/experiments/prompt-tuning/hc+ft/Results/FLICKR_QWEN/Flickr_prompt01.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UshariRanasinghe\Desktop\Projects\vlm-research\experiments\prompt-tuning\hc+ft\Results\FLICKR_QWEN\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E790A92-FE75-4F36-916D-7D45CF797E3B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="20" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="evaluation" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
   <si>
     <t>sample_index</t>
   </si>
@@ -145,12 +151,27 @@
   <si>
     <t>A woman is painting a picture of a cathedral.</t>
   </si>
+  <si>
+    <t>How many people are playing soccer in this scene?,</t>
+  </si>
+  <si>
+    <t>You are an observer describing the scene. Explain what is happening, focusing on the actions of people, animals, or objects as if you were narrating it for someone else.,</t>
+  </si>
+  <si>
+    <t>Imagine you are a guide or commentator. Describe how a &lt;text_1&gt; is interacting with a &lt;text_2&gt; in the environment, providing context and details.,</t>
+  </si>
+  <si>
+    <t>"Describe using format - Subject: ___; Activity: ___; Environment: ___; Additional Notes: ___;"</t>
+  </si>
+  <si>
+    <t>Describe using format - Subject: ___; Activity: ___; Environment: ___; Additional Notes: ___;</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,6 +186,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -202,10 +236,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -213,6 +254,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -233,7 +282,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="image_1.png"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="image_1.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -271,7 +326,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="image_2.png"/>
+        <xdr:cNvPr id="3" name="Picture 2" descr="image_2.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -309,7 +370,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3" descr="image_3.png"/>
+        <xdr:cNvPr id="4" name="Picture 3" descr="image_3.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -347,7 +414,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4" descr="image_4.png"/>
+        <xdr:cNvPr id="5" name="Picture 4" descr="image_4.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -385,7 +458,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5" descr="image_5.png"/>
+        <xdr:cNvPr id="6" name="Picture 5" descr="image_5.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -423,7 +502,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6" descr="image_6.png"/>
+        <xdr:cNvPr id="7" name="Picture 6" descr="image_6.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -461,7 +546,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7" descr="image_7.png"/>
+        <xdr:cNvPr id="8" name="Picture 7" descr="image_7.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -494,12 +585,18 @@
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>346075</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8" descr="image_8.png"/>
+        <xdr:cNvPr id="9" name="Picture 8" descr="image_8.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -532,12 +629,18 @@
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>520700</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9" descr="image_9.png"/>
+        <xdr:cNvPr id="10" name="Picture 9" descr="image_9.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -570,12 +673,18 @@
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>600075</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10" descr="image_10.png"/>
+        <xdr:cNvPr id="11" name="Picture 10" descr="image_10.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -644,7 +753,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -676,9 +785,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -710,6 +837,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -885,11 +1030,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:J11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:R13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="2:10">
+    <row r="1" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -918,7 +1063,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B2">
         <v>0</v>
       </c>
@@ -932,22 +1077,22 @@
         <v>20</v>
       </c>
       <c r="F2">
-        <v>0.5544059693813324</v>
+        <v>0.55440596938133235</v>
       </c>
       <c r="G2">
-        <v>0.1739130434782609</v>
+        <v>0.17391304347826089</v>
       </c>
       <c r="H2">
-        <v>2.850183862579191</v>
+        <v>2.8501838625791911</v>
       </c>
       <c r="I2">
         <v>6930.13623046875</v>
       </c>
       <c r="J2">
-        <v>30.32253170013428</v>
+        <v>30.322531700134281</v>
       </c>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B3">
         <v>1</v>
       </c>
@@ -961,13 +1106,13 @@
         <v>21</v>
       </c>
       <c r="F3">
-        <v>0.2920052409172058</v>
+        <v>0.29200524091720581</v>
       </c>
       <c r="G3">
         <v>0.2</v>
       </c>
       <c r="H3">
-        <v>1.73232476221268</v>
+        <v>1.7323247622126801</v>
       </c>
       <c r="I3">
         <v>6938.26123046875</v>
@@ -976,7 +1121,7 @@
         <v>1.955400228500366</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>2</v>
       </c>
@@ -990,13 +1135,13 @@
         <v>22</v>
       </c>
       <c r="F4">
-        <v>0.5776948809623719</v>
+        <v>0.57769488096237187</v>
       </c>
       <c r="G4">
-        <v>0.09090909090909091</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="H4">
-        <v>0.8537548126704519</v>
+        <v>0.85375481267045195</v>
       </c>
       <c r="I4">
         <v>6938.26123046875</v>
@@ -1005,7 +1150,7 @@
         <v>1.665047168731689</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>3</v>
       </c>
@@ -1022,7 +1167,7 @@
         <v>0.6306077241897583</v>
       </c>
       <c r="G5">
-        <v>0.08333333333333333</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="H5">
         <v>1.502331444744673</v>
@@ -1031,10 +1176,10 @@
         <v>6934.3896484375</v>
       </c>
       <c r="J5">
-        <v>1.552144765853882</v>
+        <v>1.5521447658538821</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>4</v>
       </c>
@@ -1051,19 +1196,19 @@
         <v>0.6739171504974365</v>
       </c>
       <c r="G6">
-        <v>0.4444444444444445</v>
+        <v>0.44444444444444448</v>
       </c>
       <c r="H6">
-        <v>1.674486314072423</v>
+        <v>1.6744863140724231</v>
       </c>
       <c r="I6">
         <v>6938.26123046875</v>
       </c>
       <c r="J6">
-        <v>0.9807863235473633</v>
+        <v>0.98078632354736328</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B7">
         <v>5</v>
       </c>
@@ -1077,22 +1222,22 @@
         <v>25</v>
       </c>
       <c r="F7">
-        <v>0.4451745688915253</v>
+        <v>0.44517456889152529</v>
       </c>
       <c r="G7">
-        <v>0.06060606060606061</v>
+        <v>6.0606060606060608E-2</v>
       </c>
       <c r="H7">
-        <v>1.057914095487377</v>
+        <v>1.0579140954873769</v>
       </c>
       <c r="I7">
         <v>6938.26123046875</v>
       </c>
       <c r="J7">
-        <v>1.900625228881836</v>
+        <v>1.9006252288818359</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>6</v>
       </c>
@@ -1106,10 +1251,10 @@
         <v>26</v>
       </c>
       <c r="F8">
-        <v>0.5386141896247864</v>
+        <v>0.53861418962478635</v>
       </c>
       <c r="G8">
-        <v>0.3333333333333334</v>
+        <v>0.33333333333333343</v>
       </c>
       <c r="H8">
         <v>1.661550799254621</v>
@@ -1120,8 +1265,26 @@
       <c r="J8">
         <v>1.722927331924438</v>
       </c>
+      <c r="M8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0.56840900000000005</v>
+      </c>
+      <c r="O8" s="2">
+        <v>0.42857099999999998</v>
+      </c>
+      <c r="P8" s="2">
+        <v>3.645108</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>6935.3779999999997</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0.82883899999999999</v>
+      </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B9">
         <v>7</v>
       </c>
@@ -1135,13 +1298,13 @@
         <v>27</v>
       </c>
       <c r="F9">
-        <v>0.5462295293807984</v>
+        <v>0.54622952938079838</v>
       </c>
       <c r="G9">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H9">
-        <v>2.083379478245777</v>
+        <v>2.0833794782457771</v>
       </c>
       <c r="I9">
         <v>6943.14697265625</v>
@@ -1149,8 +1312,26 @@
       <c r="J9">
         <v>1.486834049224854</v>
       </c>
+      <c r="M9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0.52560899999999999</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0.23671200000000001</v>
+      </c>
+      <c r="P9" s="2">
+        <v>1.587226</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>6939.3739999999998</v>
+      </c>
+      <c r="R9" s="2">
+        <v>1.332398</v>
+      </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>8</v>
       </c>
@@ -1164,22 +1345,40 @@
         <v>28</v>
       </c>
       <c r="F10">
-        <v>0.347679877281189</v>
+        <v>0.34767987728118899</v>
       </c>
       <c r="G10">
         <v>0.125</v>
       </c>
       <c r="H10">
-        <v>0.8965593252574335</v>
+        <v>0.89655932525743354</v>
       </c>
       <c r="I10">
         <v>6939.25</v>
       </c>
       <c r="J10">
-        <v>1.611679553985596</v>
+        <v>1.6116795539855959</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0.52903199999999995</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0.22244800000000001</v>
+      </c>
+      <c r="P10" s="2">
+        <v>1.66049</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>6945.2749999999996</v>
+      </c>
+      <c r="R10" s="2">
+        <v>1.3650249999999999</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>9</v>
       </c>
@@ -1193,10 +1392,10 @@
         <v>29</v>
       </c>
       <c r="F11">
-        <v>0.5684092402458191</v>
+        <v>0.56840924024581907</v>
       </c>
       <c r="G11">
-        <v>0.4285714285714285</v>
+        <v>0.42857142857142849</v>
       </c>
       <c r="H11">
         <v>3.645108419171355</v>
@@ -1205,11 +1404,75 @@
         <v>6935.37841796875</v>
       </c>
       <c r="J11">
-        <v>0.828838586807251</v>
+        <v>0.82883858680725098</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N11" s="2">
+        <v>0.529864</v>
+      </c>
+      <c r="O11" s="2">
+        <v>0.21899199999999999</v>
+      </c>
+      <c r="P11" s="2">
+        <v>1.6304540000000001</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>6945.0450000000001</v>
+      </c>
+      <c r="R11" s="2">
+        <v>1.2723640000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="F12">
+        <f>AVERAGE(F3:F11)</f>
+        <v>0.51337026688787679</v>
+      </c>
+      <c r="G12">
+        <f t="shared" ref="G12:J12" si="0">AVERAGE(G3:G11)</f>
+        <v>0.25846641013307681</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>1.6786010501240882</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>6938.1634657118057</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>1.5226981374952528</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N12" s="4">
+        <v>0.53120100000000003</v>
+      </c>
+      <c r="O12" s="4">
+        <v>0.22734499999999999</v>
+      </c>
+      <c r="P12" s="4">
+        <v>1.6421870000000001</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>6943.8119999999999</v>
+      </c>
+      <c r="R12" s="4">
+        <v>1.310452</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="M13" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>